--- a/artfynd/A 56314-2025 artfynd.xlsx
+++ b/artfynd/A 56314-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129000402</v>
+        <v>129000403</v>
       </c>
       <c r="B2" t="n">
-        <v>92873</v>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5966</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>689596</v>
+        <v>689744</v>
       </c>
       <c r="R2" t="n">
-        <v>7288009</v>
+        <v>7287990</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129000404</v>
+        <v>129000405</v>
       </c>
       <c r="B3" t="n">
-        <v>90585</v>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1962</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>689690</v>
+        <v>689628</v>
       </c>
       <c r="R3" t="n">
-        <v>7287983</v>
+        <v>7288031</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129000403</v>
+        <v>129000406</v>
       </c>
       <c r="B4" t="n">
-        <v>91851</v>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -898,21 +898,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -926,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>689744</v>
+        <v>689630</v>
       </c>
       <c r="R4" t="n">
-        <v>7287990</v>
+        <v>7288029</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,6 +990,218 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129000404</v>
+      </c>
+      <c r="B5" t="n">
+        <v>90932</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1962</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vaddporing</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Anomoporia kamtschatica</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Akkavare, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>689690</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7287983</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129000402</v>
+      </c>
+      <c r="B6" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Akkavare, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>689596</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7288009</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 56314-2025 artfynd.xlsx
+++ b/artfynd/A 56314-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129000403</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129000405</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129000406</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129000404</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,8 +1227,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129000402</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 56314-2025 artfynd.xlsx
+++ b/artfynd/A 56314-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ6"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1230,6 +1230,118 @@
       <c r="AZ6" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/129000402</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135619414</v>
+      </c>
+      <c r="B7" t="n">
+        <v>92027</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>2079</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Nordtagging</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Odonticium romellii</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Björkliden, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>689513</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7288330</v>
+      </c>
+      <c r="S7" t="n">
+        <v>20</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>21:20</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>21:20</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135619414</t>
         </is>
       </c>
     </row>
@@ -1240,6 +1352,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 56314-2025 artfynd.xlsx
+++ b/artfynd/A 56314-2025 artfynd.xlsx
@@ -1238,7 +1238,7 @@
         <v>135619414</v>
       </c>
       <c r="B7" t="n">
-        <v>92027</v>
+        <v>92069</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 56314-2025 artfynd.xlsx
+++ b/artfynd/A 56314-2025 artfynd.xlsx
@@ -1238,7 +1238,7 @@
         <v>135619414</v>
       </c>
       <c r="B7" t="n">
-        <v>92069</v>
+        <v>92096</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 56314-2025 artfynd.xlsx
+++ b/artfynd/A 56314-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ6"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1230,6 +1230,118 @@
       <c r="AZ6" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/129000402</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135619414</v>
+      </c>
+      <c r="B7" t="n">
+        <v>92101</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>2079</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Nordtagging</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Odonticium romellii</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Björkliden, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>689513</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7288330</v>
+      </c>
+      <c r="S7" t="n">
+        <v>20</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>21:20</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>21:20</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135619414</t>
         </is>
       </c>
     </row>
@@ -1240,6 +1352,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 56314-2025 artfynd.xlsx
+++ b/artfynd/A 56314-2025 artfynd.xlsx
@@ -1238,7 +1238,7 @@
         <v>135619414</v>
       </c>
       <c r="B7" t="n">
-        <v>92101</v>
+        <v>92103</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 56314-2025 artfynd.xlsx
+++ b/artfynd/A 56314-2025 artfynd.xlsx
@@ -1238,7 +1238,7 @@
         <v>135619414</v>
       </c>
       <c r="B7" t="n">
-        <v>92103</v>
+        <v>92117</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 56314-2025 artfynd.xlsx
+++ b/artfynd/A 56314-2025 artfynd.xlsx
@@ -1238,7 +1238,7 @@
         <v>135619414</v>
       </c>
       <c r="B7" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 56314-2025 artfynd.xlsx
+++ b/artfynd/A 56314-2025 artfynd.xlsx
@@ -1238,7 +1238,7 @@
         <v>135619414</v>
       </c>
       <c r="B7" t="n">
-        <v>92118</v>
+        <v>92119</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 56314-2025 artfynd.xlsx
+++ b/artfynd/A 56314-2025 artfynd.xlsx
@@ -1238,7 +1238,7 @@
         <v>135619414</v>
       </c>
       <c r="B7" t="n">
-        <v>92119</v>
+        <v>92120</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
